--- a/AC_2009/AC_027.xlsx
+++ b/AC_2009/AC_027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,11 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -87,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -137,11 +142,33 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +203,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -18038,235 +18082,235 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="7" t="inlineStr">
+      <c r="A261" s="16" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B261" s="8" t="inlineStr"/>
-      <c r="C261" s="9">
+      <c r="B261" s="17" t="inlineStr"/>
+      <c r="C261" s="18">
         <f>SUM(C6:C260)</f>
         <v/>
       </c>
-      <c r="D261" s="9">
+      <c r="D261" s="18">
         <f>SUM(D6:D260)</f>
         <v/>
       </c>
-      <c r="E261" s="9">
+      <c r="E261" s="18">
         <f>SUM(E6:E260)</f>
         <v/>
       </c>
-      <c r="F261" s="9">
+      <c r="F261" s="18">
         <f>SUM(F6:F260)</f>
         <v/>
       </c>
-      <c r="G261" s="9">
+      <c r="G261" s="18">
         <f>SUM(G6:G260)</f>
         <v/>
       </c>
-      <c r="H261" s="9">
+      <c r="H261" s="18">
         <f>SUM(H6:H260)</f>
         <v/>
       </c>
-      <c r="I261" s="9">
+      <c r="I261" s="18">
         <f>SUM(I6:I260)</f>
         <v/>
       </c>
-      <c r="J261" s="9">
+      <c r="J261" s="18">
         <f>SUM(J6:J260)</f>
         <v/>
       </c>
-      <c r="K261" s="9">
+      <c r="K261" s="18">
         <f>SUM(K6:K260)</f>
         <v/>
       </c>
-      <c r="L261" s="9">
+      <c r="L261" s="18">
         <f>SUM(L6:L260)</f>
         <v/>
       </c>
-      <c r="M261" s="9">
+      <c r="M261" s="18">
         <f>SUM(M6:M260)</f>
         <v/>
       </c>
-      <c r="N261" s="9">
+      <c r="N261" s="18">
         <f>SUM(N6:N260)</f>
         <v/>
       </c>
-      <c r="O261" s="9">
+      <c r="O261" s="18">
         <f>SUM(O6:O260)</f>
         <v/>
       </c>
-      <c r="P261" s="9">
+      <c r="P261" s="18">
         <f>SUM(P6:P260)</f>
         <v/>
       </c>
-      <c r="Q261" s="9">
+      <c r="Q261" s="18">
         <f>SUM(Q6:Q260)</f>
         <v/>
       </c>
-      <c r="R261" s="9">
+      <c r="R261" s="18">
         <f>SUM(R6:R260)</f>
         <v/>
       </c>
-      <c r="S261" s="9">
+      <c r="S261" s="18">
         <f>SUM(S6:S260)</f>
         <v/>
       </c>
-      <c r="T261" s="9">
+      <c r="T261" s="18">
         <f>SUM(T6:T260)</f>
         <v/>
       </c>
-      <c r="U261" s="9">
-        <f>SUM(C261:P261)-Q261</f>
+      <c r="U261" s="18">
+        <f>SUM(U6:U260)</f>
         <v/>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="10" t="inlineStr">
+      <c r="A262" s="19" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr"/>
-      <c r="C262" s="12" t="n">
+      <c r="C262" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="D262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="12" t="n">
+      <c r="D262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="G262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" s="12" t="n">
+      <c r="G262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="I262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K262" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q262" s="12" t="n">
+      <c r="I262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q262" s="18" t="n">
         <v>113</v>
       </c>
-      <c r="R262" s="12" t="n">
+      <c r="R262" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="S262" s="12" t="n">
+      <c r="S262" s="18" t="n">
         <v>145</v>
       </c>
-      <c r="T262" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U262" s="12" t="n">
+      <c r="T262" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="13" t="inlineStr">
+      <c r="A263" s="20" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B263" s="14" t="inlineStr"/>
-      <c r="C263" s="15">
+      <c r="B263" s="21" t="inlineStr"/>
+      <c r="C263" s="22">
         <f>C261+C262</f>
         <v/>
       </c>
-      <c r="D263" s="15">
+      <c r="D263" s="22">
         <f>D261+D262</f>
         <v/>
       </c>
-      <c r="E263" s="15">
+      <c r="E263" s="22">
         <f>E261+E262</f>
         <v/>
       </c>
-      <c r="F263" s="15">
+      <c r="F263" s="22">
         <f>F261+F262</f>
         <v/>
       </c>
-      <c r="G263" s="15">
+      <c r="G263" s="22">
         <f>G261+G262</f>
         <v/>
       </c>
-      <c r="H263" s="15">
+      <c r="H263" s="22">
         <f>H261+H262</f>
         <v/>
       </c>
-      <c r="I263" s="15">
+      <c r="I263" s="22">
         <f>I261+I262</f>
         <v/>
       </c>
-      <c r="J263" s="15">
+      <c r="J263" s="22">
         <f>J261+J262</f>
         <v/>
       </c>
-      <c r="K263" s="15">
+      <c r="K263" s="22">
         <f>K261+K262</f>
         <v/>
       </c>
-      <c r="L263" s="15">
+      <c r="L263" s="22">
         <f>L261+L262</f>
         <v/>
       </c>
-      <c r="M263" s="15">
+      <c r="M263" s="22">
         <f>M261+M262</f>
         <v/>
       </c>
-      <c r="N263" s="15">
+      <c r="N263" s="22">
         <f>N261+N262</f>
         <v/>
       </c>
-      <c r="O263" s="15">
+      <c r="O263" s="22">
         <f>O261+O262</f>
         <v/>
       </c>
-      <c r="P263" s="15">
+      <c r="P263" s="22">
         <f>P261+P262</f>
         <v/>
       </c>
-      <c r="Q263" s="15">
+      <c r="Q263" s="22">
         <f>Q261+Q262</f>
         <v/>
       </c>
-      <c r="R263" s="15">
+      <c r="R263" s="22">
         <f>R261+R262</f>
         <v/>
       </c>
-      <c r="S263" s="15">
+      <c r="S263" s="22">
         <f>S261+S262</f>
         <v/>
       </c>
-      <c r="T263" s="15">
+      <c r="T263" s="22">
         <f>T261+T262</f>
         <v/>
       </c>
-      <c r="U263" s="15">
-        <f>SUM(C263:P263)-Q263</f>
+      <c r="U263" s="22">
+        <f>U261+U262</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_027.xlsx
+++ b/AC_2009/AC_027.xlsx
@@ -1435,15 +1435,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U263"/>
+  <dimension ref="A1:T263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
     <col width="28" customWidth="1" style="1" min="2" max="2"/>
     <col width="16" customWidth="1" style="1" min="3" max="16"/>
     <col width="18" customWidth="1" style="1" min="17" max="17"/>
-    <col width="15" customWidth="1" style="1" min="18" max="21"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="22" max="16384"/>
+    <col width="15" customWidth="1" style="1" min="18" max="20"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="23">
@@ -1471,7 +1471,6 @@
       <c r="R1" s="3" t="n"/>
       <c r="S1" s="3" t="n"/>
       <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="23">
       <c r="A2" s="4" t="inlineStr">
@@ -1498,7 +1497,6 @@
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
-      <c r="U2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="23">
       <c r="A3" s="4" t="inlineStr">
@@ -1525,7 +1523,6 @@
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="23">
       <c r="A4" s="5" t="n"/>
@@ -1548,7 +1545,6 @@
       <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="5" t="n"/>
-      <c r="U4" s="5" t="n"/>
     </row>
     <row r="5" ht="26.55" customHeight="1" s="23">
       <c r="A5" s="6" t="inlineStr">
@@ -1651,11 +1647,6 @@
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="13.55" customHeight="1" s="23">
       <c r="A6" s="7" t="n">
@@ -1720,9 +1711,6 @@
       <c r="T6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="13.55" customHeight="1" s="23">
       <c r="A7" s="7" t="n">
@@ -1787,9 +1775,6 @@
       <c r="T7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="13.55" customHeight="1" s="23">
       <c r="A8" s="7" t="n">
@@ -1854,9 +1839,6 @@
       <c r="T8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="13.55" customHeight="1" s="23">
       <c r="A9" s="7" t="n">
@@ -1921,9 +1903,6 @@
       <c r="T9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="23">
       <c r="A10" s="7" t="n">
@@ -1988,9 +1967,6 @@
       <c r="T10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="13.55" customHeight="1" s="23">
       <c r="A11" s="7" t="n">
@@ -2053,9 +2029,6 @@
         <v>525</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2122,9 +2095,6 @@
       <c r="T12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="23">
       <c r="A13" s="7" t="n">
@@ -2189,9 +2159,6 @@
       <c r="T13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="13.55" customHeight="1" s="23">
       <c r="A14" s="7" t="n">
@@ -2256,9 +2223,6 @@
       <c r="T14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="13.55" customHeight="1" s="23">
       <c r="A15" s="7" t="n">
@@ -2323,9 +2287,6 @@
       <c r="T15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="13.55" customHeight="1" s="23">
       <c r="A16" s="7" t="n">
@@ -2390,9 +2351,6 @@
       <c r="T16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="13.55" customHeight="1" s="23">
       <c r="A17" s="7" t="n">
@@ -2457,9 +2415,6 @@
       <c r="T17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="13.55" customHeight="1" s="23">
       <c r="A18" s="7" t="n">
@@ -2524,9 +2479,6 @@
       <c r="T18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="13.55" customHeight="1" s="23">
       <c r="A19" s="7" t="n">
@@ -2591,9 +2543,6 @@
       <c r="T19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="23">
       <c r="A20" s="7" t="n">
@@ -2658,9 +2607,6 @@
       <c r="T20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="13.55" customHeight="1" s="23">
       <c r="A21" s="7" t="n">
@@ -2725,9 +2671,6 @@
       <c r="T21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="13.55" customHeight="1" s="23">
       <c r="A22" s="7" t="n">
@@ -2792,9 +2735,6 @@
       <c r="T22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="23">
       <c r="A23" s="7" t="n">
@@ -2859,9 +2799,6 @@
       <c r="T23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="13.55" customHeight="1" s="23">
       <c r="A24" s="7" t="n">
@@ -2926,9 +2863,6 @@
       <c r="T24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="23">
       <c r="A25" s="7" t="n">
@@ -2993,9 +2927,6 @@
       <c r="T25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="13.55" customHeight="1" s="23">
       <c r="A26" s="7" t="n">
@@ -3060,9 +2991,6 @@
       <c r="T26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="13.55" customHeight="1" s="23">
       <c r="A27" s="7" t="n">
@@ -3127,9 +3055,6 @@
       <c r="T27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="13.55" customHeight="1" s="23">
       <c r="A28" s="7" t="n">
@@ -3194,9 +3119,6 @@
       <c r="T28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="13.55" customHeight="1" s="23">
       <c r="A29" s="7" t="n">
@@ -3261,9 +3183,6 @@
       <c r="T29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="13.55" customHeight="1" s="23">
       <c r="A30" s="7" t="n">
@@ -3328,9 +3247,6 @@
       <c r="T30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="13.55" customHeight="1" s="23">
       <c r="A31" s="7" t="n">
@@ -3395,9 +3311,6 @@
       <c r="T31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="13.55" customHeight="1" s="23">
       <c r="A32" s="7" t="n">
@@ -3462,9 +3375,6 @@
       <c r="T32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="13.55" customHeight="1" s="23">
       <c r="A33" s="7" t="n">
@@ -3529,9 +3439,6 @@
       <c r="T33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="13.55" customHeight="1" s="23">
       <c r="A34" s="7" t="n">
@@ -3596,9 +3503,6 @@
       <c r="T34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" ht="13.55" customHeight="1" s="23">
       <c r="A35" s="7" t="n">
@@ -3663,9 +3567,6 @@
       <c r="T35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="13.55" customHeight="1" s="23">
       <c r="A36" s="7" t="n">
@@ -3730,9 +3631,6 @@
       <c r="T36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="13.55" customHeight="1" s="23">
       <c r="A37" s="7" t="n">
@@ -3797,9 +3695,6 @@
       <c r="T37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="13.55" customHeight="1" s="23">
       <c r="A38" s="7" t="n">
@@ -3864,9 +3759,6 @@
       <c r="T38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="13.55" customHeight="1" s="23">
       <c r="A39" s="7" t="n">
@@ -3931,9 +3823,6 @@
       <c r="T39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" ht="13.55" customHeight="1" s="23">
       <c r="A40" s="7" t="n">
@@ -3998,9 +3887,6 @@
       <c r="T40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" ht="13.55" customHeight="1" s="23">
       <c r="A41" s="7" t="n">
@@ -4065,9 +3951,6 @@
       <c r="T41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U41" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" ht="13.55" customHeight="1" s="23">
       <c r="A42" s="7" t="n">
@@ -4132,9 +4015,6 @@
       <c r="T42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U42" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" ht="13.55" customHeight="1" s="23">
       <c r="A43" s="7" t="n">
@@ -4199,9 +4079,6 @@
       <c r="T43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" ht="13.55" customHeight="1" s="23">
       <c r="A44" s="7" t="n">
@@ -4266,9 +4143,6 @@
       <c r="T44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" ht="13.55" customHeight="1" s="23">
       <c r="A45" s="7" t="n">
@@ -4333,9 +4207,6 @@
       <c r="T45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" ht="13.55" customHeight="1" s="23">
       <c r="A46" s="7" t="n">
@@ -4400,9 +4271,6 @@
       <c r="T46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" ht="13.55" customHeight="1" s="23">
       <c r="A47" s="7" t="n">
@@ -4467,9 +4335,6 @@
       <c r="T47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" ht="13.55" customHeight="1" s="23">
       <c r="A48" s="7" t="n">
@@ -4534,9 +4399,6 @@
       <c r="T48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49" ht="13.55" customHeight="1" s="23">
       <c r="A49" s="7" t="n">
@@ -4601,9 +4463,6 @@
       <c r="T49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50" ht="13.55" customHeight="1" s="23">
       <c r="A50" s="7" t="n">
@@ -4668,9 +4527,6 @@
       <c r="T50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51" ht="13.55" customHeight="1" s="23">
       <c r="A51" s="7" t="n">
@@ -4735,9 +4591,6 @@
       <c r="T51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52" ht="13.55" customHeight="1" s="23">
       <c r="A52" s="7" t="n">
@@ -4802,9 +4655,6 @@
       <c r="T52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" ht="13.55" customHeight="1" s="23">
       <c r="A53" s="7" t="n">
@@ -4869,9 +4719,6 @@
       <c r="T53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" ht="13.55" customHeight="1" s="23">
       <c r="A54" s="7" t="n">
@@ -4936,9 +4783,6 @@
       <c r="T54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" ht="13.55" customHeight="1" s="23">
       <c r="A55" s="7" t="n">
@@ -5003,9 +4847,6 @@
       <c r="T55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56" ht="13.55" customHeight="1" s="23">
       <c r="A56" s="7" t="n">
@@ -5070,9 +4911,6 @@
       <c r="T56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57" ht="13.55" customHeight="1" s="23">
       <c r="A57" s="7" t="n">
@@ -5137,9 +4975,6 @@
       <c r="T57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" ht="13.55" customHeight="1" s="23">
       <c r="A58" s="7" t="n">
@@ -5204,9 +5039,6 @@
       <c r="T58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59" ht="13.55" customHeight="1" s="23">
       <c r="A59" s="7" t="n">
@@ -5271,9 +5103,6 @@
       <c r="T59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60" ht="13.55" customHeight="1" s="23">
       <c r="A60" s="7" t="n">
@@ -5338,9 +5167,6 @@
       <c r="T60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61" ht="13.55" customHeight="1" s="23">
       <c r="A61" s="7" t="n">
@@ -5405,9 +5231,6 @@
       <c r="T61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62" ht="13.55" customHeight="1" s="23">
       <c r="A62" s="7" t="n">
@@ -5472,9 +5295,6 @@
       <c r="T62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63" ht="13.55" customHeight="1" s="23">
       <c r="A63" s="7" t="n">
@@ -5539,9 +5359,6 @@
       <c r="T63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64" ht="13.55" customHeight="1" s="23">
       <c r="A64" s="7" t="n">
@@ -5606,9 +5423,6 @@
       <c r="T64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65" ht="13.55" customHeight="1" s="23">
       <c r="A65" s="7" t="n">
@@ -5673,9 +5487,6 @@
       <c r="T65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" ht="13.55" customHeight="1" s="23">
       <c r="A66" s="7" t="n">
@@ -5740,9 +5551,6 @@
       <c r="T66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" ht="13.55" customHeight="1" s="23">
       <c r="A67" s="7" t="n">
@@ -5807,9 +5615,6 @@
       <c r="T67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" ht="13.55" customHeight="1" s="23">
       <c r="A68" s="7" t="n">
@@ -5874,9 +5679,6 @@
       <c r="T68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U68" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" ht="13.55" customHeight="1" s="23">
       <c r="A69" s="7" t="n">
@@ -5941,9 +5743,6 @@
       <c r="T69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U69" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" ht="13.55" customHeight="1" s="23">
       <c r="A70" s="7" t="n">
@@ -6008,9 +5807,6 @@
       <c r="T70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="23">
       <c r="A71" s="7" t="n">
@@ -6075,9 +5871,6 @@
       <c r="T71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" ht="13.55" customHeight="1" s="23">
       <c r="A72" s="7" t="n">
@@ -6142,9 +5935,6 @@
       <c r="T72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" ht="13.55" customHeight="1" s="23">
       <c r="A73" s="7" t="n">
@@ -6209,9 +5999,6 @@
       <c r="T73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" ht="13.55" customHeight="1" s="23">
       <c r="A74" s="7" t="n">
@@ -6276,9 +6063,6 @@
       <c r="T74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" ht="13.55" customHeight="1" s="23">
       <c r="A75" s="7" t="n">
@@ -6343,9 +6127,6 @@
       <c r="T75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U75" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" ht="13.55" customHeight="1" s="23">
       <c r="A76" s="7" t="n">
@@ -6410,9 +6191,6 @@
       <c r="T76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" ht="13.55" customHeight="1" s="23">
       <c r="A77" s="7" t="n">
@@ -6477,9 +6255,6 @@
       <c r="T77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" ht="13.55" customHeight="1" s="23">
       <c r="A78" s="7" t="n">
@@ -6544,9 +6319,6 @@
       <c r="T78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="23">
       <c r="A79" s="7" t="n">
@@ -6611,9 +6383,6 @@
       <c r="T79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" ht="13.55" customHeight="1" s="23">
       <c r="A80" s="7" t="n">
@@ -6678,9 +6447,6 @@
       <c r="T80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U80" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" ht="13.55" customHeight="1" s="23">
       <c r="A81" s="7" t="n">
@@ -6745,9 +6511,6 @@
       <c r="T81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U81" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" ht="13.55" customHeight="1" s="23">
       <c r="A82" s="7" t="n">
@@ -6812,9 +6575,6 @@
       <c r="T82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" ht="13.55" customHeight="1" s="23">
       <c r="A83" s="7" t="n">
@@ -6879,9 +6639,6 @@
       <c r="T83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U83" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" ht="13.55" customHeight="1" s="23">
       <c r="A84" s="7" t="n">
@@ -6946,9 +6703,6 @@
       <c r="T84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" ht="13.55" customHeight="1" s="23">
       <c r="A85" s="7" t="n">
@@ -7013,9 +6767,6 @@
       <c r="T85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" ht="13.55" customHeight="1" s="23">
       <c r="A86" s="7" t="n">
@@ -7080,9 +6831,6 @@
       <c r="T86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" ht="13.55" customHeight="1" s="23">
       <c r="A87" s="7" t="n">
@@ -7147,9 +6895,6 @@
       <c r="T87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88" ht="13.55" customHeight="1" s="23">
       <c r="A88" s="7" t="n">
@@ -7214,9 +6959,6 @@
       <c r="T88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" ht="13.55" customHeight="1" s="23">
       <c r="A89" s="7" t="n">
@@ -7281,9 +7023,6 @@
       <c r="T89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" ht="13.55" customHeight="1" s="23">
       <c r="A90" s="7" t="n">
@@ -7348,9 +7087,6 @@
       <c r="T90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" ht="13.55" customHeight="1" s="23">
       <c r="A91" s="7" t="n">
@@ -7415,9 +7151,6 @@
       <c r="T91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U91" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" ht="13.55" customHeight="1" s="23">
       <c r="A92" s="7" t="n">
@@ -7482,9 +7215,6 @@
       <c r="T92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93" ht="13.55" customHeight="1" s="23">
       <c r="A93" s="7" t="n">
@@ -7549,9 +7279,6 @@
       <c r="T93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U93" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94" ht="13.55" customHeight="1" s="23">
       <c r="A94" s="7" t="n">
@@ -7616,9 +7343,6 @@
       <c r="T94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95" ht="13.55" customHeight="1" s="23">
       <c r="A95" s="7" t="n">
@@ -7683,9 +7407,6 @@
       <c r="T95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U95" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96" ht="13.55" customHeight="1" s="23">
       <c r="A96" s="7" t="n">
@@ -7750,9 +7471,6 @@
       <c r="T96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97" ht="13.55" customHeight="1" s="23">
       <c r="A97" s="7" t="n">
@@ -7817,9 +7535,6 @@
       <c r="T97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98" ht="13.55" customHeight="1" s="23">
       <c r="A98" s="7" t="n">
@@ -7884,9 +7599,6 @@
       <c r="T98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99" ht="13.55" customHeight="1" s="23">
       <c r="A99" s="7" t="n">
@@ -7951,9 +7663,6 @@
       <c r="T99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" ht="13.55" customHeight="1" s="23">
       <c r="A100" s="7" t="n">
@@ -8018,9 +7727,6 @@
       <c r="T100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101" ht="13.55" customHeight="1" s="23">
       <c r="A101" s="7" t="n">
@@ -8085,9 +7791,6 @@
       <c r="T101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" ht="13.55" customHeight="1" s="23">
       <c r="A102" s="7" t="n">
@@ -8152,9 +7855,6 @@
       <c r="T102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103" ht="13.55" customHeight="1" s="23">
       <c r="A103" s="7" t="n">
@@ -8219,9 +7919,6 @@
       <c r="T103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" ht="13.55" customHeight="1" s="23">
       <c r="A104" s="7" t="n">
@@ -8286,9 +7983,6 @@
       <c r="T104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" ht="13.55" customHeight="1" s="23">
       <c r="A105" s="7" t="n">
@@ -8353,9 +8047,6 @@
       <c r="T105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" ht="13.55" customHeight="1" s="23">
       <c r="A106" s="7" t="n">
@@ -8420,9 +8111,6 @@
       <c r="T106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" ht="13.55" customHeight="1" s="23">
       <c r="A107" s="7" t="n">
@@ -8487,9 +8175,6 @@
       <c r="T107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" ht="13.55" customHeight="1" s="23">
       <c r="A108" s="7" t="n">
@@ -8554,9 +8239,6 @@
       <c r="T108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" ht="13.55" customHeight="1" s="23">
       <c r="A109" s="7" t="n">
@@ -8621,9 +8303,6 @@
       <c r="T109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110" ht="13.55" customHeight="1" s="23">
       <c r="A110" s="7" t="n">
@@ -8688,9 +8367,6 @@
       <c r="T110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" ht="13.55" customHeight="1" s="23">
       <c r="A111" s="7" t="n">
@@ -8755,9 +8431,6 @@
       <c r="T111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" ht="13.55" customHeight="1" s="23">
       <c r="A112" s="7" t="n">
@@ -8822,9 +8495,6 @@
       <c r="T112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" ht="13.55" customHeight="1" s="23">
       <c r="A113" s="7" t="n">
@@ -8889,9 +8559,6 @@
       <c r="T113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U113" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" ht="13.55" customHeight="1" s="23">
       <c r="A114" s="7" t="n">
@@ -8956,9 +8623,6 @@
       <c r="T114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" ht="13.55" customHeight="1" s="23">
       <c r="A115" s="7" t="n">
@@ -9023,9 +8687,6 @@
       <c r="T115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" ht="13.55" customHeight="1" s="23">
       <c r="A116" s="7" t="n">
@@ -9090,9 +8751,6 @@
       <c r="T116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117" ht="13.55" customHeight="1" s="23">
       <c r="A117" s="7" t="n">
@@ -9157,9 +8815,6 @@
       <c r="T117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="118" ht="13.55" customHeight="1" s="23">
       <c r="A118" s="7" t="n">
@@ -9224,9 +8879,6 @@
       <c r="T118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119" ht="13.55" customHeight="1" s="23">
       <c r="A119" s="7" t="n">
@@ -9291,9 +8943,6 @@
       <c r="T119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120" ht="13.55" customHeight="1" s="23">
       <c r="A120" s="7" t="n">
@@ -9358,9 +9007,6 @@
       <c r="T120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="121" ht="13.55" customHeight="1" s="23">
       <c r="A121" s="7" t="n">
@@ -9425,9 +9071,6 @@
       <c r="T121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122" ht="13.55" customHeight="1" s="23">
       <c r="A122" s="7" t="n">
@@ -9492,9 +9135,6 @@
       <c r="T122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123" ht="13.55" customHeight="1" s="23">
       <c r="A123" s="7" t="n">
@@ -9559,9 +9199,6 @@
       <c r="T123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124" ht="13.55" customHeight="1" s="23">
       <c r="A124" s="7" t="n">
@@ -9626,9 +9263,6 @@
       <c r="T124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" ht="13.55" customHeight="1" s="23">
       <c r="A125" s="7" t="n">
@@ -9693,9 +9327,6 @@
       <c r="T125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="126" ht="13.55" customHeight="1" s="23">
       <c r="A126" s="7" t="n">
@@ -9760,9 +9391,6 @@
       <c r="T126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U126" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="127" ht="13.55" customHeight="1" s="23">
       <c r="A127" s="7" t="n">
@@ -9827,9 +9455,6 @@
       <c r="T127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128" ht="13.55" customHeight="1" s="23">
       <c r="A128" s="7" t="n">
@@ -9894,9 +9519,6 @@
       <c r="T128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129" ht="13.55" customHeight="1" s="23">
       <c r="A129" s="7" t="n">
@@ -9961,9 +9583,6 @@
       <c r="T129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" ht="13.55" customHeight="1" s="23">
       <c r="A130" s="7" t="n">
@@ -10028,9 +9647,6 @@
       <c r="T130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131" ht="13.55" customHeight="1" s="23">
       <c r="A131" s="7" t="n">
@@ -10095,9 +9711,6 @@
       <c r="T131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" ht="13.55" customHeight="1" s="23">
       <c r="A132" s="7" t="n">
@@ -10162,9 +9775,6 @@
       <c r="T132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" ht="13.55" customHeight="1" s="23">
       <c r="A133" s="7" t="n">
@@ -10229,9 +9839,6 @@
       <c r="T133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" ht="13.55" customHeight="1" s="23">
       <c r="A134" s="7" t="n">
@@ -10296,9 +9903,6 @@
       <c r="T134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U134" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" ht="13.55" customHeight="1" s="23">
       <c r="A135" s="7" t="n">
@@ -10363,9 +9967,6 @@
       <c r="T135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" ht="13.55" customHeight="1" s="23">
       <c r="A136" s="7" t="n">
@@ -10430,9 +10031,6 @@
       <c r="T136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" ht="13.55" customHeight="1" s="23">
       <c r="A137" s="7" t="n">
@@ -10497,9 +10095,6 @@
       <c r="T137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" ht="13.55" customHeight="1" s="23">
       <c r="A138" s="7" t="n">
@@ -10564,9 +10159,6 @@
       <c r="T138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U138" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" ht="13.55" customHeight="1" s="23">
       <c r="A139" s="7" t="n">
@@ -10631,9 +10223,6 @@
       <c r="T139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U139" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" ht="13.55" customHeight="1" s="23">
       <c r="A140" s="7" t="n">
@@ -10698,9 +10287,6 @@
       <c r="T140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U140" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" ht="13.55" customHeight="1" s="23">
       <c r="A141" s="7" t="n">
@@ -10765,9 +10351,6 @@
       <c r="T141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U141" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" ht="13.55" customHeight="1" s="23">
       <c r="A142" s="7" t="n">
@@ -10832,9 +10415,6 @@
       <c r="T142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" ht="13.55" customHeight="1" s="23">
       <c r="A143" s="7" t="n">
@@ -10899,9 +10479,6 @@
       <c r="T143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U143" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" ht="13.55" customHeight="1" s="23">
       <c r="A144" s="7" t="n">
@@ -10966,9 +10543,6 @@
       <c r="T144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" ht="13.55" customHeight="1" s="23">
       <c r="A145" s="7" t="n">
@@ -11033,9 +10607,6 @@
       <c r="T145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="146" ht="13.55" customHeight="1" s="23">
       <c r="A146" s="7" t="n">
@@ -11100,9 +10671,6 @@
       <c r="T146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147" ht="13.55" customHeight="1" s="23">
       <c r="A147" s="7" t="n">
@@ -11167,9 +10735,6 @@
       <c r="T147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148" ht="13.55" customHeight="1" s="23">
       <c r="A148" s="7" t="n">
@@ -11234,9 +10799,6 @@
       <c r="T148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U148" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="149" ht="13.55" customHeight="1" s="23">
       <c r="A149" s="7" t="n">
@@ -11301,9 +10863,6 @@
       <c r="T149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U149" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" ht="13.55" customHeight="1" s="23">
       <c r="A150" s="7" t="n">
@@ -11368,9 +10927,6 @@
       <c r="T150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151" ht="13.55" customHeight="1" s="23">
       <c r="A151" s="7" t="n">
@@ -11435,9 +10991,6 @@
       <c r="T151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="152" ht="13.55" customHeight="1" s="23">
       <c r="A152" s="7" t="n">
@@ -11502,9 +11055,6 @@
       <c r="T152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U152" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="153" ht="13.55" customHeight="1" s="23">
       <c r="A153" s="7" t="n">
@@ -11569,9 +11119,6 @@
       <c r="T153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U153" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="154" ht="13.55" customHeight="1" s="23">
       <c r="A154" s="7" t="n">
@@ -11636,9 +11183,6 @@
       <c r="T154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="155" ht="13.55" customHeight="1" s="23">
       <c r="A155" s="7" t="n">
@@ -11703,9 +11247,6 @@
       <c r="T155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U155" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="156" ht="13.55" customHeight="1" s="23">
       <c r="A156" s="7" t="n">
@@ -11770,9 +11311,6 @@
       <c r="T156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="157" ht="13.55" customHeight="1" s="23">
       <c r="A157" s="7" t="n">
@@ -11837,9 +11375,6 @@
       <c r="T157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U157" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158" ht="13.55" customHeight="1" s="23">
       <c r="A158" s="7" t="n">
@@ -11904,9 +11439,6 @@
       <c r="T158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U158" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="159" ht="13.55" customHeight="1" s="23">
       <c r="A159" s="7" t="n">
@@ -11971,9 +11503,6 @@
       <c r="T159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U159" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160" ht="13.55" customHeight="1" s="23">
       <c r="A160" s="7" t="n">
@@ -12038,9 +11567,6 @@
       <c r="T160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U160" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="161" ht="13.55" customHeight="1" s="23">
       <c r="A161" s="7" t="n">
@@ -12105,9 +11631,6 @@
       <c r="T161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U161" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="162" ht="13.55" customHeight="1" s="23">
       <c r="A162" s="7" t="n">
@@ -12172,9 +11695,6 @@
       <c r="T162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U162" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="163" ht="13.55" customHeight="1" s="23">
       <c r="A163" s="7" t="n">
@@ -12239,9 +11759,6 @@
       <c r="T163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U163" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164" ht="13.55" customHeight="1" s="23">
       <c r="A164" s="7" t="n">
@@ -12306,9 +11823,6 @@
       <c r="T164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U164" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="165" ht="13.55" customHeight="1" s="23">
       <c r="A165" s="7" t="n">
@@ -12373,9 +11887,6 @@
       <c r="T165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U165" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="166" ht="13.55" customHeight="1" s="23">
       <c r="A166" s="7" t="n">
@@ -12440,9 +11951,6 @@
       <c r="T166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U166" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="167" ht="13.55" customHeight="1" s="23">
       <c r="A167" s="7" t="n">
@@ -12507,9 +12015,6 @@
       <c r="T167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U167" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168" ht="13.55" customHeight="1" s="23">
       <c r="A168" s="7" t="n">
@@ -12574,9 +12079,6 @@
       <c r="T168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U168" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="169" ht="13.55" customHeight="1" s="23">
       <c r="A169" s="7" t="n">
@@ -12641,9 +12143,6 @@
       <c r="T169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U169" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170" ht="13.55" customHeight="1" s="23">
       <c r="A170" s="7" t="n">
@@ -12708,9 +12207,6 @@
       <c r="T170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U170" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171" ht="13.55" customHeight="1" s="23">
       <c r="A171" s="7" t="n">
@@ -12775,9 +12271,6 @@
       <c r="T171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U171" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172" ht="13.55" customHeight="1" s="23">
       <c r="A172" s="7" t="n">
@@ -12842,9 +12335,6 @@
       <c r="T172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U172" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173" ht="13.55" customHeight="1" s="23">
       <c r="A173" s="7" t="n">
@@ -12909,9 +12399,6 @@
       <c r="T173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U173" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="174" ht="13.55" customHeight="1" s="23">
       <c r="A174" s="7" t="n">
@@ -12976,9 +12463,6 @@
       <c r="T174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U174" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="175" ht="13.55" customHeight="1" s="23">
       <c r="A175" s="7" t="n">
@@ -13043,9 +12527,6 @@
       <c r="T175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U175" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="176" ht="13.55" customHeight="1" s="23">
       <c r="A176" s="7" t="n">
@@ -13110,9 +12591,6 @@
       <c r="T176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="177" ht="13.55" customHeight="1" s="23">
       <c r="A177" s="7" t="n">
@@ -13177,9 +12655,6 @@
       <c r="T177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U177" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" ht="13.55" customHeight="1" s="23">
       <c r="A178" s="7" t="n">
@@ -13244,9 +12719,6 @@
       <c r="T178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U178" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="179" ht="13.55" customHeight="1" s="23">
       <c r="A179" s="7" t="n">
@@ -13311,9 +12783,6 @@
       <c r="T179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U179" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" ht="13.55" customHeight="1" s="23">
       <c r="A180" s="7" t="n">
@@ -13378,9 +12847,6 @@
       <c r="T180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="181" ht="13.55" customHeight="1" s="23">
       <c r="A181" s="7" t="n">
@@ -13445,9 +12911,6 @@
       <c r="T181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U181" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="182" ht="13.55" customHeight="1" s="23">
       <c r="A182" s="7" t="n">
@@ -13512,9 +12975,6 @@
       <c r="T182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U182" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" ht="13.55" customHeight="1" s="23">
       <c r="A183" s="7" t="n">
@@ -13579,9 +13039,6 @@
       <c r="T183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U183" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" ht="13.55" customHeight="1" s="23">
       <c r="A184" s="7" t="n">
@@ -13646,9 +13103,6 @@
       <c r="T184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U184" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="185" ht="13.55" customHeight="1" s="23">
       <c r="A185" s="7" t="n">
@@ -13713,9 +13167,6 @@
       <c r="T185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U185" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="186" ht="13.55" customHeight="1" s="23">
       <c r="A186" s="7" t="n">
@@ -13780,9 +13231,6 @@
       <c r="T186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U186" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="187" ht="13.55" customHeight="1" s="23">
       <c r="A187" s="7" t="n">
@@ -13847,9 +13295,6 @@
       <c r="T187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U187" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="188" ht="13.55" customHeight="1" s="23">
       <c r="A188" s="7" t="n">
@@ -13914,9 +13359,6 @@
       <c r="T188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U188" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="189" ht="13.55" customHeight="1" s="23">
       <c r="A189" s="7" t="n">
@@ -13981,9 +13423,6 @@
       <c r="T189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U189" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="190" ht="13.55" customHeight="1" s="23">
       <c r="A190" s="7" t="n">
@@ -14048,9 +13487,6 @@
       <c r="T190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U190" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="191" ht="13.55" customHeight="1" s="23">
       <c r="A191" s="7" t="n">
@@ -14115,9 +13551,6 @@
       <c r="T191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U191" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="192" ht="13.55" customHeight="1" s="23">
       <c r="A192" s="7" t="n">
@@ -14182,9 +13615,6 @@
       <c r="T192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U192" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="193" ht="13.55" customHeight="1" s="23">
       <c r="A193" s="7" t="n">
@@ -14249,9 +13679,6 @@
       <c r="T193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U193" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="194" ht="13.55" customHeight="1" s="23">
       <c r="A194" s="7" t="n">
@@ -14316,9 +13743,6 @@
       <c r="T194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U194" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="23">
       <c r="A195" s="7" t="n">
@@ -14383,9 +13807,6 @@
       <c r="T195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U195" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="196" ht="13.55" customHeight="1" s="23">
       <c r="A196" s="7" t="n">
@@ -14450,9 +13871,6 @@
       <c r="T196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U196" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="197" ht="13.55" customHeight="1" s="23">
       <c r="A197" s="7" t="n">
@@ -14517,9 +13935,6 @@
       <c r="T197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U197" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="23">
       <c r="A198" s="7" t="n">
@@ -14584,9 +13999,6 @@
       <c r="T198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U198" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="23">
       <c r="A199" s="7" t="n">
@@ -14651,9 +14063,6 @@
       <c r="T199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U199" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="23">
       <c r="A200" s="7" t="n">
@@ -14718,9 +14127,6 @@
       <c r="T200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U200" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" ht="13.55" customHeight="1" s="23">
       <c r="A201" s="7" t="n">
@@ -14785,9 +14191,6 @@
       <c r="T201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U201" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="202" ht="13.55" customHeight="1" s="23">
       <c r="A202" s="7" t="n">
@@ -14852,9 +14255,6 @@
       <c r="T202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U202" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="203" ht="13.55" customHeight="1" s="23">
       <c r="A203" s="7" t="n">
@@ -14919,9 +14319,6 @@
       <c r="T203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U203" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="204" ht="13.55" customHeight="1" s="23">
       <c r="A204" s="7" t="n">
@@ -14986,9 +14383,6 @@
       <c r="T204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U204" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="205" ht="13.55" customHeight="1" s="23">
       <c r="A205" s="7" t="n">
@@ -15053,9 +14447,6 @@
       <c r="T205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U205" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="206" ht="13.55" customHeight="1" s="23">
       <c r="A206" s="7" t="n">
@@ -15120,9 +14511,6 @@
       <c r="T206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U206" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="207" ht="13.55" customHeight="1" s="23">
       <c r="A207" s="7" t="n">
@@ -15187,9 +14575,6 @@
       <c r="T207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U207" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="208" ht="13.55" customHeight="1" s="23">
       <c r="A208" s="7" t="n">
@@ -15254,9 +14639,6 @@
       <c r="T208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U208" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" ht="13.55" customHeight="1" s="23">
       <c r="A209" s="7" t="n">
@@ -15321,9 +14703,6 @@
       <c r="T209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U209" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="210" ht="13.55" customHeight="1" s="23">
       <c r="A210" s="7" t="n">
@@ -15388,9 +14767,6 @@
       <c r="T210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U210" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="23">
       <c r="A211" s="7" t="n">
@@ -15455,9 +14831,6 @@
       <c r="T211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U211" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="212" ht="13.55" customHeight="1" s="23">
       <c r="A212" s="7" t="n">
@@ -15522,9 +14895,6 @@
       <c r="T212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U212" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="213" ht="13.55" customHeight="1" s="23">
       <c r="A213" s="7" t="n">
@@ -15589,9 +14959,6 @@
       <c r="T213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U213" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="214" ht="13.55" customHeight="1" s="23">
       <c r="A214" s="7" t="n">
@@ -15656,9 +15023,6 @@
       <c r="T214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U214" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="215" ht="13.55" customHeight="1" s="23">
       <c r="A215" s="7" t="n">
@@ -15723,9 +15087,6 @@
       <c r="T215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U215" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="216" ht="13.55" customHeight="1" s="23">
       <c r="A216" s="7" t="n">
@@ -15790,9 +15151,6 @@
       <c r="T216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U216" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="217" ht="13.55" customHeight="1" s="23">
       <c r="A217" s="7" t="n">
@@ -15857,9 +15215,6 @@
       <c r="T217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U217" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="218" ht="13.55" customHeight="1" s="23">
       <c r="A218" s="7" t="n">
@@ -15924,9 +15279,6 @@
       <c r="T218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U218" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="219" ht="13.55" customHeight="1" s="23">
       <c r="A219" s="7" t="n">
@@ -15991,9 +15343,6 @@
       <c r="T219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U219" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="220" ht="13.55" customHeight="1" s="23">
       <c r="A220" s="7" t="n">
@@ -16058,9 +15407,6 @@
       <c r="T220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U220" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="221" ht="13.55" customHeight="1" s="23">
       <c r="A221" s="7" t="n">
@@ -16125,9 +15471,6 @@
       <c r="T221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U221" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="222" ht="13.55" customHeight="1" s="23">
       <c r="A222" s="7" t="n">
@@ -16192,9 +15535,6 @@
       <c r="T222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U222" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="223" ht="13.55" customHeight="1" s="23">
       <c r="A223" s="7" t="n">
@@ -16259,9 +15599,6 @@
       <c r="T223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U223" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="224" ht="13.55" customHeight="1" s="23">
       <c r="A224" s="7" t="n">
@@ -16326,9 +15663,6 @@
       <c r="T224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U224" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="225" ht="13.55" customHeight="1" s="23">
       <c r="A225" s="7" t="n">
@@ -16393,9 +15727,6 @@
       <c r="T225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U225" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="226" ht="13.55" customHeight="1" s="23">
       <c r="A226" s="7" t="n">
@@ -16460,9 +15791,6 @@
       <c r="T226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U226" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="227" ht="13.55" customHeight="1" s="23">
       <c r="A227" s="7" t="n">
@@ -16527,9 +15855,6 @@
       <c r="T227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U227" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="228" ht="13.55" customHeight="1" s="23">
       <c r="A228" s="7" t="n">
@@ -16594,9 +15919,6 @@
       <c r="T228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U228" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="229" ht="13.55" customHeight="1" s="23">
       <c r="A229" s="7" t="n">
@@ -16661,9 +15983,6 @@
       <c r="T229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U229" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="230" ht="13.55" customHeight="1" s="23">
       <c r="A230" s="7" t="n">
@@ -16728,9 +16047,6 @@
       <c r="T230" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U230" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="231" ht="13.55" customHeight="1" s="23">
       <c r="A231" s="7" t="n">
@@ -16795,9 +16111,6 @@
       <c r="T231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U231" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="232" ht="13.55" customHeight="1" s="23">
       <c r="A232" s="7" t="n">
@@ -16862,9 +16175,6 @@
       <c r="T232" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U232" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="233" ht="13.55" customHeight="1" s="23">
       <c r="A233" s="7" t="n">
@@ -16929,9 +16239,6 @@
       <c r="T233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U233" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="234" ht="13.55" customHeight="1" s="23">
       <c r="A234" s="7" t="n">
@@ -16996,9 +16303,6 @@
       <c r="T234" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U234" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="235" ht="13.55" customHeight="1" s="23">
       <c r="A235" s="7" t="n">
@@ -17063,9 +16367,6 @@
       <c r="T235" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U235" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="236" ht="13.55" customHeight="1" s="23">
       <c r="A236" s="7" t="n">
@@ -17130,9 +16431,6 @@
       <c r="T236" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U236" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="237" ht="13.55" customHeight="1" s="23">
       <c r="A237" s="7" t="n">
@@ -17197,9 +16495,6 @@
       <c r="T237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U237" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="238" ht="13.55" customHeight="1" s="23">
       <c r="A238" s="7" t="n">
@@ -17264,9 +16559,6 @@
       <c r="T238" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U238" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="239" ht="13.55" customHeight="1" s="23">
       <c r="A239" s="7" t="n">
@@ -17331,9 +16623,6 @@
       <c r="T239" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U239" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="240" ht="13.55" customHeight="1" s="23">
       <c r="A240" s="7" t="n">
@@ -17398,9 +16687,6 @@
       <c r="T240" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U240" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="241" ht="13.55" customHeight="1" s="23">
       <c r="A241" s="7" t="n">
@@ -17465,9 +16751,6 @@
       <c r="T241" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U241" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="242" ht="13.55" customHeight="1" s="23">
       <c r="A242" s="7" t="n">
@@ -17532,9 +16815,6 @@
       <c r="T242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U242" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="243" ht="13.55" customHeight="1" s="23">
       <c r="A243" s="7" t="n">
@@ -17599,9 +16879,6 @@
       <c r="T243" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U243" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="244" ht="13.55" customHeight="1" s="23">
       <c r="A244" s="7" t="n">
@@ -17666,9 +16943,6 @@
       <c r="T244" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U244" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="245" ht="13.55" customHeight="1" s="23">
       <c r="A245" s="7" t="n">
@@ -17733,9 +17007,6 @@
       <c r="T245" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U245" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="246" ht="13.55" customHeight="1" s="23">
       <c r="A246" s="7" t="n">
@@ -17800,9 +17071,6 @@
       <c r="T246" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U246" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="247" ht="13.55" customHeight="1" s="23">
       <c r="A247" s="7" t="n">
@@ -17867,9 +17135,6 @@
       <c r="T247" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U247" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="248" ht="13.55" customHeight="1" s="23">
       <c r="A248" s="7" t="n">
@@ -17934,9 +17199,6 @@
       <c r="T248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U248" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="249" ht="13.55" customHeight="1" s="23">
       <c r="A249" s="7" t="n">
@@ -18001,9 +17263,6 @@
       <c r="T249" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U249" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="250" ht="13.55" customHeight="1" s="23">
       <c r="A250" s="7" t="n">
@@ -18068,9 +17327,6 @@
       <c r="T250" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U250" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="251" ht="13.55" customHeight="1" s="23">
       <c r="A251" s="7" t="n">
@@ -18135,9 +17391,6 @@
       <c r="T251" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U251" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="252" ht="13.55" customHeight="1" s="23">
       <c r="A252" s="7" t="n">
@@ -18202,9 +17455,6 @@
       <c r="T252" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U252" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="253" ht="13.55" customHeight="1" s="23">
       <c r="A253" s="7" t="n">
@@ -18269,9 +17519,6 @@
       <c r="T253" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U253" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="254" ht="13.55" customHeight="1" s="23">
       <c r="A254" s="7" t="n">
@@ -18336,9 +17583,6 @@
       <c r="T254" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U254" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="255" ht="13.55" customHeight="1" s="23">
       <c r="A255" s="7" t="n">
@@ -18403,9 +17647,6 @@
       <c r="T255" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U255" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="256" ht="13.55" customHeight="1" s="23">
       <c r="A256" s="7" t="n">
@@ -18470,9 +17711,6 @@
       <c r="T256" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U256" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="257" ht="13.55" customHeight="1" s="23">
       <c r="A257" s="7" t="n">
@@ -18537,9 +17775,6 @@
       <c r="T257" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U257" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="258" ht="13.55" customHeight="1" s="23">
       <c r="A258" s="7" t="n">
@@ -18604,9 +17839,6 @@
       <c r="T258" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U258" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="259" ht="13.55" customHeight="1" s="23">
       <c r="A259" s="7" t="n">
@@ -18671,9 +17903,6 @@
       <c r="T259" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U259" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="260" ht="14.05" customHeight="1" s="23">
       <c r="A260" s="10" t="n">
@@ -18738,9 +17967,6 @@
       <c r="T260" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U260" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="261" ht="14.15" customHeight="1" s="23">
       <c r="A261" s="13" t="inlineStr">
@@ -18803,9 +18029,6 @@
       <c r="T261" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U261" s="15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="262" ht="13.65" customHeight="1" s="23">
       <c r="A262" s="16" t="inlineStr">
@@ -18868,9 +18091,6 @@
       <c r="T262" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U262" s="15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="263" ht="13.65" customHeight="1" s="23">
       <c r="A263" s="18" t="inlineStr">
@@ -18930,10 +18150,7 @@
       <c r="S263" s="21" t="n">
         <v>138796</v>
       </c>
-      <c r="T263" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" s="22" t="n">
+      <c r="T263" s="22" t="n">
         <v>0</v>
       </c>
     </row>
